--- a/data/trans_bre/P8_2_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P8_2_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,41; 13,23</t>
+          <t>5,54; 13,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 15,23</t>
+          <t>6,15; 14,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,39; 14,14</t>
+          <t>5,42; 13,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 7,87</t>
+          <t>-1,14; 7,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,47; 112,97</t>
+          <t>34,2; 107,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,13; 108,25</t>
+          <t>31,01; 99,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,11; 105,82</t>
+          <t>29,51; 102,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 52,41</t>
+          <t>-5,45; 50,62</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,64; 13,47</t>
+          <t>6,23; 13,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 12,55</t>
+          <t>4,96; 12,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,52; 13,7</t>
+          <t>6,43; 13,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,14; 11,61</t>
+          <t>-38,84; 11,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45,16; 118,58</t>
+          <t>41,05; 117,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,19; 84,55</t>
+          <t>28,22; 86,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,78; 107,2</t>
+          <t>39,05; 103,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,34; 99,74</t>
+          <t>-64,3; 100,72</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,81; 13,83</t>
+          <t>5,13; 13,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 14,75</t>
+          <t>6,54; 14,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,64; 11,33</t>
+          <t>3,24; 11,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 5,22</t>
+          <t>-10,47; 5,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,61; 101,8</t>
+          <t>29,84; 101,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,2; 138,22</t>
+          <t>45,76; 133,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,07; 90,33</t>
+          <t>19,22; 90,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-52,49; 30,46</t>
+          <t>-55,8; 31,88</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,56; 12,18</t>
+          <t>5,66; 12,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,6; 14,37</t>
+          <t>7,1; 14,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,92; 9,87</t>
+          <t>2,86; 10,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 10,75</t>
+          <t>2,43; 11,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,23; 97,71</t>
+          <t>37,53; 103,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,96; 98,15</t>
+          <t>37,98; 97,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,26; 78,32</t>
+          <t>16,85; 78,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,09; 78,75</t>
+          <t>16,8; 81,98</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,52; 11,12</t>
+          <t>7,27; 11,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,1; 12,09</t>
+          <t>8,19; 12,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,43; 10,14</t>
+          <t>6,48; 10,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,54; 6,48</t>
+          <t>-17,84; 6,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>50,68; 84,71</t>
+          <t>48,79; 84,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,81; 82,53</t>
+          <t>50,46; 83,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,05; 73,47</t>
+          <t>42,13; 76,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-51,74; 42,99</t>
+          <t>-46,99; 44,65</t>
         </is>
       </c>
     </row>
